--- a/SLVH_Build_Tracker.xlsx
+++ b/SLVH_Build_Tracker.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/988e9a16b3672765/Desktop/SLVH/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="2" documentId="11_13A3ABDCF9A82DDE4D1C754B50C5F65CEA0DB047" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{526B9FE3-32E4-4A8D-AB8E-248D1BCED30C}"/>
+  <xr:revisionPtr revIDLastSave="3" documentId="11_13A3ABDCF9A82DDE4D1C754B50C5F65CEA0DB047" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00B489B0-8593-4C8D-881B-AB7BB0E8F730}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10300" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -3820,8 +3820,8 @@
       <c r="L9" s="21" t="s">
         <v>54</v>
       </c>
-      <c r="M9" s="22" t="s">
-        <v>35</v>
+      <c r="M9" s="12" t="s">
+        <v>26</v>
       </c>
       <c r="N9" s="13" t="s">
         <v>55</v>
